--- a/data/trans_dic/P1421-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1421-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,45</t>
+          <t>0,38; 3,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,08</t>
+          <t>0,63; 3,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,15</t>
+          <t>0,23; 2,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,5</t>
+          <t>1,01; 7,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,14</t>
+          <t>1,92; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,11</t>
+          <t>1,84; 5,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,0</t>
+          <t>1,18; 3,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,26; 15,46</t>
+          <t>6,56; 15,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,28</t>
+          <t>1,39; 3,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,65</t>
+          <t>1,5; 3,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,58</t>
+          <t>0,83; 2,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 9,52</t>
+          <t>4,18; 9,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,36</t>
+          <t>1,21; 3,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,01</t>
+          <t>0,49; 2,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,84</t>
+          <t>0,18; 1,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,84</t>
+          <t>2,57; 7,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,65; 9,88</t>
+          <t>5,62; 10,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,54</t>
+          <t>2,25; 5,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,06</t>
+          <t>4,92; 8,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 13,02</t>
+          <t>7,91; 13,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,93</t>
+          <t>3,52; 5,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,23</t>
+          <t>1,56; 3,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,83</t>
+          <t>2,66; 4,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,73</t>
+          <t>5,75; 9,55</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,46</t>
+          <t>1,19; 3,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,02</t>
+          <t>0,88; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,39</t>
+          <t>0,46; 2,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,19</t>
+          <t>3,21; 7,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,31</t>
+          <t>4,37; 8,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,24</t>
+          <t>5,3; 9,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,75</t>
+          <t>1,85; 4,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,37; 12,78</t>
+          <t>8,58; 12,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,38</t>
+          <t>3,15; 5,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,65</t>
+          <t>3,34; 5,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,18</t>
+          <t>1,41; 2,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 9,74</t>
+          <t>6,45; 9,14</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,79</t>
+          <t>1,52; 4,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,17</t>
+          <t>0,34; 2,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,13</t>
+          <t>0,95; 3,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,4</t>
+          <t>4,5; 8,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,31</t>
+          <t>4,21; 8,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,88</t>
+          <t>3,82; 7,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,67; 7,32</t>
+          <t>3,68; 7,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,54</t>
+          <t>12,51; 16,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,36; 5,93</t>
+          <t>3,16; 5,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,51</t>
+          <t>2,32; 4,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,81</t>
+          <t>2,68; 4,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 11,51</t>
+          <t>9,19; 11,97</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,79</t>
+          <t>2,36; 6,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,34</t>
+          <t>0,25; 2,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,95</t>
+          <t>1,12; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,14</t>
+          <t>2,84; 5,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,1</t>
+          <t>3,56; 8,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,36</t>
+          <t>3,22; 7,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 9,69</t>
+          <t>4,85; 9,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,99; 14,26</t>
+          <t>10,42; 14,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,58</t>
+          <t>3,47; 6,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,54</t>
+          <t>2,0; 4,36</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 6,44</t>
+          <t>3,41; 6,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,64</t>
+          <t>7,07; 9,62</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,48</t>
+          <t>1,09; 4,55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,67</t>
+          <t>0,32; 2,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,02</t>
+          <t>0,3; 2,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,51</t>
+          <t>2,08; 5,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,51</t>
+          <t>4,85; 10,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 9,35</t>
+          <t>4,13; 9,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,36; 9,35</t>
+          <t>4,31; 9,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,54</t>
+          <t>7,09; 11,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,95</t>
+          <t>3,62; 7,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 5,7</t>
+          <t>2,67; 5,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,52</t>
+          <t>2,67; 5,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,67</t>
+          <t>5,11; 7,69</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,71</t>
+          <t>0,93; 5,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,75</t>
+          <t>1,02; 4,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,21</t>
+          <t>2,45; 6,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,06</t>
+          <t>1,75; 6,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,95</t>
+          <t>4,19; 9,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,05</t>
+          <t>6,13; 12,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,19</t>
+          <t>8,21; 12,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,14</t>
+          <t>1,84; 5,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,07</t>
+          <t>2,71; 6,11</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,44</t>
+          <t>4,52; 8,48</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,42; 9,38</t>
+          <t>6,36; 9,22</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,0</t>
+          <t>1,95; 3,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,63</t>
+          <t>0,88; 1,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,85</t>
+          <t>1,05; 1,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,28</t>
+          <t>3,78; 5,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,65</t>
+          <t>4,98; 6,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,68; 6,13</t>
+          <t>4,57; 6,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,37</t>
+          <t>4,69; 6,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 11,77</t>
+          <t>10,44; 12,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,65; 4,59</t>
+          <t>3,64; 4,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,77</t>
+          <t>2,89; 3,77</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,04</t>
+          <t>3,06; 3,95</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,41</t>
+          <t>7,51; 8,66</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>36979</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44733</t>
+          <t>49818</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1853; 12107</t>
+          <t>1898; 14969</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3146; 13980</t>
+          <t>2880; 14651</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>974; 9017</t>
+          <t>964; 9851</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4392; 29997</t>
+          <t>4096; 28833</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9014; 24008</t>
+          <t>8996; 24181</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8009; 26285</t>
+          <t>7906; 24199</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4258; 15814</t>
+          <t>4652; 15311</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19603; 48410</t>
+          <t>23777; 55165</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13068; 31545</t>
+          <t>13372; 31334</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13537; 32245</t>
+          <t>13259; 33620</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6914; 21062</t>
+          <t>6778; 21353</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28981; 67851</t>
+          <t>32100; 73997</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>21903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49161</t>
+          <t>52486</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69315</t>
+          <t>74390</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8916; 24714</t>
+          <t>8896; 23712</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3607; 13838</t>
+          <t>3356; 13886</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1050; 10878</t>
+          <t>1041; 10634</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11348; 33225</t>
+          <t>12237; 35355</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35341; 61814</t>
+          <t>35131; 62614</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14215; 33790</t>
+          <t>13707; 32739</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27259; 51063</t>
+          <t>27702; 50154</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29823; 66597</t>
+          <t>39625; 68531</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48750; 80681</t>
+          <t>47854; 79118</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19723; 41919</t>
+          <t>20210; 40479</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30811; 55717</t>
+          <t>30688; 54381</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51646; 90949</t>
+          <t>56246; 93424</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56693</t>
+          <t>65103</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86997</t>
+          <t>95872</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8049; 22090</t>
+          <t>7607; 22432</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5395; 20599</t>
+          <t>5969; 20973</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3168; 15963</t>
+          <t>3059; 15713</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20470; 43923</t>
+          <t>19932; 43971</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31610; 57329</t>
+          <t>30123; 56368</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37829; 65568</t>
+          <t>37636; 64928</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12033; 31401</t>
+          <t>12248; 30964</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45226; 69034</t>
+          <t>53185; 78714</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41363; 71440</t>
+          <t>41804; 70249</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47200; 78672</t>
+          <t>46450; 78273</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18133; 42358</t>
+          <t>18749; 39198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72033; 104824</t>
+          <t>79986; 113465</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41062</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>104173</t>
+          <t>107487</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>145235</t>
+          <t>151040</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8464; 24857</t>
+          <t>7884; 23927</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2953; 13364</t>
+          <t>2064; 12421</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6099; 20216</t>
+          <t>6166; 19657</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18009; 65574</t>
+          <t>31491; 58801</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21888; 42861</t>
+          <t>21712; 42232</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23503; 48394</t>
+          <t>23466; 47920</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23829; 47510</t>
+          <t>23869; 47976</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>86707; 124822</t>
+          <t>92016; 121379</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34727; 61346</t>
+          <t>32689; 60251</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28993; 55417</t>
+          <t>28527; 55276</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34624; 62240</t>
+          <t>34657; 62705</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90288; 183963</t>
+          <t>131840; 171868</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>25489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>65948</t>
+          <t>74802</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89671</t>
+          <t>100291</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9321; 26243</t>
+          <t>9107; 26227</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1044; 10041</t>
+          <t>1056; 9834</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5237; 18876</t>
+          <t>5363; 19854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16340; 34390</t>
+          <t>17297; 36177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14266; 32723</t>
+          <t>14388; 33137</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13522; 32979</t>
+          <t>14417; 33066</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23649; 48154</t>
+          <t>24107; 48735</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54427; 77659</t>
+          <t>63211; 88646</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27516; 52027</t>
+          <t>27467; 52322</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17851; 39765</t>
+          <t>17492; 38176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33895; 62777</t>
+          <t>33218; 63314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>76686; 106526</t>
+          <t>85867; 116890</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>38895</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48140</t>
+          <t>52480</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3588; 13102</t>
+          <t>3198; 13320</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>985; 8281</t>
+          <t>981; 8426</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1009; 10112</t>
+          <t>1004; 9648</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7901; 20238</t>
+          <t>8457; 21017</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16463; 36056</t>
+          <t>16643; 35005</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15446; 33089</t>
+          <t>14618; 32695</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16487; 35331</t>
+          <t>16298; 34973</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14420; 58053</t>
+          <t>31122; 49080</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22643; 44169</t>
+          <t>22991; 45064</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17816; 37860</t>
+          <t>17715; 36937</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>19142; 39311</t>
+          <t>19026; 40385</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24929; 65129</t>
+          <t>43158; 64994</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>43402</t>
+          <t>46703</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>54736</t>
+          <t>58828</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1948; 11980</t>
+          <t>1955; 11823</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 7721</t>
+          <t>0; 7305</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2631; 12218</t>
+          <t>2633; 12310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7270; 17557</t>
+          <t>7588; 18702</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5847; 20247</t>
+          <t>5849; 20991</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15081; 34815</t>
+          <t>16318; 36615</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23834; 48214</t>
+          <t>24527; 48540</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>34862; 51836</t>
+          <t>38105; 56966</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9925; 27970</t>
+          <t>10015; 27296</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17515; 38793</t>
+          <t>17318; 39014</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28830; 55493</t>
+          <t>29692; 55734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>45432; 66424</t>
+          <t>49223; 71406</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152702</t>
+          <t>160263</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>386125</t>
+          <t>422455</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>538827</t>
+          <t>582717</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>62800; 98230</t>
+          <t>63733; 98843</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30012; 55803</t>
+          <t>30091; 56183</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>35392; 62858</t>
+          <t>35615; 64238</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>115766; 182537</t>
+          <t>133411; 188991</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>170511; 224671</t>
+          <t>168324; 222270</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>166549; 217776</t>
+          <t>162510; 218997</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>169038; 225855</t>
+          <t>166148; 223414</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>325032; 430155</t>
+          <t>389366; 457124</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>243028; 305286</t>
+          <t>241953; 304359</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>202730; 263268</t>
+          <t>201953; 262877</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>211957; 280336</t>
+          <t>212211; 273862</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>470235; 597952</t>
+          <t>545152; 628725</t>
         </is>
       </c>
     </row>
